--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513649_FASEFINALAFFA1_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513649_FASEFINALAFFA1_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0637</v>
+        <v>5.3504</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2164</v>
+        <v>3.1134</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8474</v>
+        <v>2.2369</v>
       </c>
       <c r="G2" t="n">
         <v>4.198</v>
@@ -610,13 +610,13 @@
         <v>2.7263</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4126</v>
+        <v>-0.126</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9709</v>
+        <v>-0.0738</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4417</v>
+        <v>-0.0522</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2795</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5941</v>
+        <v>2.207</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8619</v>
+        <v>3.3636</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2679</v>
+        <v>-1.1566</v>
       </c>
       <c r="G3" t="n">
         <v>1.7566</v>
@@ -688,13 +688,13 @@
         <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0848</v>
+        <v>0.6977</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4093</v>
+        <v>0.9109</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3245</v>
+        <v>-0.2132</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2211</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6595</v>
+        <v>1.488</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4973</v>
+        <v>0.1453</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1568</v>
+        <v>1.3426</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.6803</v>
+        <v>4.5576</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.539</v>
+        <v>2.4806</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1413</v>
+        <v>2.077</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.5462</v>
+        <v>4.3719</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.8299</v>
+        <v>1.9963</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2837</v>
+        <v>2.3756</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1341</v>
+        <v>0.1857</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2909</v>
+        <v>0.4843</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4249</v>
+        <v>-0.2986</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5579</v>
+        <v>-2.5316</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1947</v>
+        <v>-5.0631</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7526</v>
+        <v>2.5316</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7819</v>
+        <v>0.4035</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2436</v>
+        <v>-0.0018</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5382</v>
+        <v>0.4054</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9416</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.8384</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2484</v>
+        <v>1.0816</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1777</v>
+        <v>-1.2379</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4261</v>
+        <v>2.3195</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5576</v>
+        <v>0.3755</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4806</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>2.077</v>
+        <v>-0.2479</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3719</v>
+        <v>-0.4273</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9963</v>
+        <v>0.0668</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3756</v>
+        <v>-0.494</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1857</v>
+        <v>0.8028</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4843</v>
+        <v>0.5567</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2986</v>
+        <v>0.2461</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.5316</v>
+        <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.0631</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5316</v>
+        <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.164</v>
+        <v>0.0897</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3249</v>
+        <v>-0.1486</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4888</v>
+        <v>0.2383</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9416</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8384</v>
+        <v>-0.6621</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.78</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3706</v>
+        <v>0.3079</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6985</v>
+        <v>0.3079</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0691</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3755</v>
+        <v>0.3079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.3079</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2479</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4273</v>
+        <v>0.3079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0668</v>
+        <v>0.3079</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.494</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8028</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5567</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2461</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6212</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6091</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0121</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9416</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3079</v>
+        <v>0.2029</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3079</v>
+        <v>-1.7313</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.9342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3079</v>
+        <v>-2.6803</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3079</v>
+        <v>-2.539</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.1413</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3079</v>
+        <v>-2.5462</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3079</v>
+        <v>-2.8299</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2837</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.1341</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.2909</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.4249</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.7526</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.3253</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.0097</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4094</v>
+        <v>-0.2611</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4458</v>
+        <v>-0.0471</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0364</v>
+        <v>-0.214</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3866</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4514</v>
+        <v>0.5997</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2999</v>
+        <v>0.0988</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7513</v>
+        <v>0.5009</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2795</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6576</v>
+        <v>-1.0781</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2135</v>
+        <v>-1.3742</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.2961</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5261</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.1187</v>
+        <v>-1.0145</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5926</v>
+        <v>0.4071</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.596</v>
+        <v>-0.6561</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.2845</v>
+        <v>-0.6645</v>
       </c>
       <c r="L9" t="n">
-        <v>3.6885</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9301</v>
+        <v>0.0487</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8341</v>
+        <v>-0.35</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9041</v>
+        <v>0.3987</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1947</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.5316</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3368</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0632</v>
+        <v>0.503</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4135</v>
+        <v>0.4504</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.0526</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5005</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0897</v>
+        <v>-1.1112</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2745</v>
+        <v>-1.3889</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1848</v>
+        <v>0.2777</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-1.5261</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0145</v>
+        <v>-6.1187</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4071</v>
+        <v>4.5926</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6561</v>
+        <v>-0.596</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6645</v>
+        <v>-4.2845</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008399999999999999</v>
+        <v>3.6885</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0487</v>
+        <v>-0.9301</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.35</v>
+        <v>-1.8341</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3987</v>
+        <v>0.9041</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1684</v>
+        <v>-2.5316</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1947</v>
+        <v>2.3368</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4914</v>
+        <v>0.6096</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5501</v>
+        <v>0.2381</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0587</v>
+        <v>0.3714</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3054</v>
+        <v>-1.2219</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9334</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.372</v>
+        <v>-0.2885</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0519</v>
@@ -1312,13 +1312,13 @@
         <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4483</v>
+        <v>-0.3648</v>
       </c>
       <c r="T11" t="n">
         <v>-0.371</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0772</v>
+        <v>0.0062</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.857</v>
+        <v>-2.122</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3081</v>
+        <v>-2.5453</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4512</v>
+        <v>0.4233</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7687</v>
@@ -1390,13 +1390,13 @@
         <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0619</v>
+        <v>-0.3269</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.263</v>
+        <v>-0.5002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2011</v>
+        <v>0.1733</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6404</v>
+        <v>-2.8414</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7281</v>
+        <v>-3.0682</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0877</v>
+        <v>0.2269</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3348</v>
@@ -1468,13 +1468,13 @@
         <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5782</v>
+        <v>0.2208</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5537</v>
+        <v>0.1062</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0245</v>
+        <v>0.1147</v>
       </c>
       <c r="V13" t="n">
         <v>0.0516</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6866</v>
+        <v>-3.7855</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.6494</v>
+        <v>-5.5257</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9628</v>
+        <v>1.7402</v>
       </c>
       <c r="G14" t="n">
         <v>-2.7548</v>
@@ -1546,13 +1546,13 @@
         <v>2.3368</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7634</v>
+        <v>0.6645</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3931</v>
+        <v>-0.2695</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1566</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5005</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.401900000000001</v>
+        <v>-1.783400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.5401</v>
+        <v>-10.9218</v>
       </c>
       <c r="F15" t="n">
-        <v>9.138300000000001</v>
+        <v>9.138299999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.915</v>
+        <v>-2.915000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>-10.3884</v>
@@ -1600,7 +1600,7 @@
         <v>1.5311</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.843</v>
+        <v>-4.843000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>6.374200000000001</v>
@@ -1624,22 +1624,22 @@
         <v>17.5261</v>
       </c>
       <c r="S15" t="n">
-        <v>3.677899999999999</v>
+        <v>4.2961</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8308999999999997</v>
+        <v>1.4492</v>
       </c>
       <c r="U15" t="n">
         <v>2.847</v>
       </c>
       <c r="V15" t="n">
-        <v>-5.112200000000001</v>
+        <v>-5.1122</v>
       </c>
       <c r="W15" t="n">
         <v>1.6768</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.789</v>
+        <v>-6.789000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3741</v>
+        <v>6.1648</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8691</v>
+        <v>4.1713</v>
       </c>
       <c r="F16" t="n">
-        <v>1.505</v>
+        <v>1.9934</v>
       </c>
       <c r="G16" t="n">
         <v>3.9301</v>
@@ -1702,13 +1702,13 @@
         <v>2.5316</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4419</v>
+        <v>0.2326</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5279</v>
+        <v>-0.1698</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.4024</v>
       </c>
       <c r="V16" t="n">
         <v>3.56</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1947</v>
+        <v>4.4544</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5815</v>
+        <v>0.3866</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6132</v>
+        <v>4.0679</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2046</v>
+        <v>1.5371</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8405</v>
+        <v>3.0717</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3641</v>
+        <v>-1.5346</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0832</v>
+        <v>0.6091</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7995</v>
+        <v>2.0912</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2837</v>
+        <v>-1.4821</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1214</v>
+        <v>0.928</v>
       </c>
       <c r="N17" t="n">
-        <v>1.041</v>
+        <v>0.9804</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0804</v>
+        <v>-0.0525</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1158</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1158</v>
+        <v>2.5316</v>
       </c>
       <c r="S17" t="n">
-        <v>1.218</v>
+        <v>0.1384</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9451000000000001</v>
+        <v>-0.7494</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2729</v>
+        <v>0.8878</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2279</v>
+        <v>1.2211</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3311</v>
+        <v>1.5005</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1032</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2235</v>
+        <v>4.2349</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.4153</v>
       </c>
       <c r="F18" t="n">
-        <v>4.136</v>
+        <v>4.6502</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5371</v>
+        <v>4.2046</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0717</v>
+        <v>3.8405</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5346</v>
+        <v>0.3641</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6091</v>
+        <v>3.0832</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0912</v>
+        <v>2.7995</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4821</v>
+        <v>0.2837</v>
       </c>
       <c r="M18" t="n">
-        <v>0.928</v>
+        <v>1.1214</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9804</v>
+        <v>1.041</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0525</v>
+        <v>0.0804</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9737</v>
+        <v>-3.1158</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5316</v>
+        <v>3.1158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0925</v>
+        <v>0.2582</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0484</v>
+        <v>-0.0517</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9559</v>
+        <v>0.3098</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2211</v>
+        <v>-0.2279</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5005</v>
+        <v>-0.3311</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2795</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3049</v>
+        <v>0.6348</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0205</v>
+        <v>-2.0837</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2844</v>
+        <v>2.7185</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4192</v>
+        <v>-0.5896</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0205</v>
+        <v>0.9749</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3987</v>
+        <v>-1.5644</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0205</v>
+        <v>-1.5346</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>-0.9595</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3987</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.9344</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3987</v>
+        <v>-0.9893</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.7526</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.921</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1144</v>
+        <v>-0.2487</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.6017</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1144</v>
+        <v>0.353</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0027</v>
+        <v>0.5653</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2831</v>
+        <v>0.1202</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2858</v>
+        <v>0.4451</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5896</v>
+        <v>0.4192</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9749</v>
+        <v>0.0205</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5644</v>
+        <v>0.3987</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5346</v>
+        <v>0.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9595</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.3987</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9344</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9893</v>
+        <v>0.3987</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7526</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.921</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8808</v>
+        <v>0.1461</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8011</v>
+        <v>0.0997</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0798</v>
+        <v>0.0464</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3371</v>
+        <v>-1.2815</v>
       </c>
       <c r="E22" t="n">
         <v>-0.8295</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.452</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1887</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1484</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1855</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0371</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8898</v>
+        <v>-2.174</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8698</v>
+        <v>-1.8487</v>
       </c>
       <c r="F23" t="n">
-        <v>0.98</v>
+        <v>-0.3253</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9623</v>
+        <v>0.4945</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2129</v>
+        <v>0.5577</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1753</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5835</v>
+        <v>2.3286</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.295</v>
+        <v>0.4721</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2885</v>
+        <v>1.8565</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6212</v>
+        <v>-1.8341</v>
       </c>
       <c r="N23" t="n">
-        <v>0.508</v>
+        <v>0.0856</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1132</v>
+        <v>-1.9197</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9737</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9474</v>
+        <v>-4.0895</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9737</v>
+        <v>1.7526</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2332</v>
+        <v>-0.6112</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6183</v>
+        <v>-0.3673</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6149</v>
+        <v>-0.2439</v>
       </c>
       <c r="V23" t="n">
         <v>0.2795</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>V. VINOS ALTEMIR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0217</v>
+        <v>-2.6024</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3471</v>
+        <v>-3.8751</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6746</v>
+        <v>1.2727</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4945</v>
+        <v>-2.8149</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5577</v>
+        <v>0.3396</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-3.1545</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3286</v>
+        <v>-2.3717</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4721</v>
+        <v>0.2053</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8565</v>
+        <v>-2.577</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8341</v>
+        <v>-0.4432</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0856</v>
+        <v>0.1343</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.9197</v>
+        <v>-0.5775</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3368</v>
+        <v>0.3895</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.0895</v>
+        <v>-1.1684</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7526</v>
+        <v>1.5579</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4589</v>
+        <v>-0.177</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8657</v>
+        <v>-0.335</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.158</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O. STUMER</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6602</v>
+        <v>-2.6132</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7105</v>
+        <v>-3.6704</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9497</v>
+        <v>1.0572</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.0308</v>
+        <v>-0.9623</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2948</v>
+        <v>0.2129</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.736</v>
+        <v>-1.1753</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.248</v>
+        <v>-1.5835</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.329</v>
+        <v>-0.295</v>
       </c>
       <c r="L25" t="n">
-        <v>0.08110000000000001</v>
+        <v>-1.2885</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7829</v>
+        <v>0.6212</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9658</v>
+        <v>0.508</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8171</v>
+        <v>0.1132</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7789</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1299</v>
+        <v>-0.9566</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2317</v>
+        <v>-0.419</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3616</v>
+        <v>-0.5376</v>
       </c>
       <c r="V25" t="n">
         <v>0.2795</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V. VINOS ALTEMIR</t>
+          <t>O. STUMER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7051</v>
+        <v>-3.9036</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.5729</v>
+        <v>-2.0095</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8678</v>
+        <v>-1.8941</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.8149</v>
+        <v>-3.0308</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3396</v>
+        <v>-2.2948</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.1545</v>
+        <v>-0.736</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.3717</v>
+        <v>-1.248</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2053</v>
+        <v>-1.329</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.577</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4432</v>
+        <v>-1.7829</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1343</v>
+        <v>-0.9658</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5775</v>
+        <v>-0.8171</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3895</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1684</v>
+        <v>-0.9737</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5579</v>
+        <v>0.1947</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2796</v>
+        <v>-0.3733</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0327</v>
+        <v>-0.0674</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2469</v>
+        <v>-0.306</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2.4018</v>
+        <v>4.3953</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.138499999999999</v>
+        <v>-9.138300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>11.5403</v>
+        <v>13.5336</v>
       </c>
       <c r="G27" t="n">
-        <v>2.915</v>
+        <v>2.915000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>10.3885</v>
@@ -2536,7 +2536,7 @@
         <v>4.446</v>
       </c>
       <c r="K27" t="n">
-        <v>5.545400000000002</v>
+        <v>5.5454</v>
       </c>
       <c r="L27" t="n">
         <v>-1.0993</v>
@@ -2548,7 +2548,7 @@
         <v>4.8431</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.374199999999999</v>
+        <v>-6.3742</v>
       </c>
       <c r="P27" t="n">
         <v>-1.9473</v>
@@ -2560,13 +2560,13 @@
         <v>15.5789</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.6778</v>
+        <v>-1.6843</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.847</v>
+        <v>-2.8471</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8308999999999999</v>
+        <v>1.1627</v>
       </c>
       <c r="V27" t="n">
         <v>5.1122</v>
